--- a/JsonConverter/ExcelFiles/RobbyDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/RobbyDialogue.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294937190" windowHeight="13140"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25545" windowHeight="7755"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -19,103 +14,131 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
-  <x:si>
-    <x:t>Sound/Voice_Pug_1_I_WantToEatPizza</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다만 아직 야근이 남아 있습니다. 좀 더 고생해주세요.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Texture2D/Texture2D_Loading_1</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+  <x:si>
+    <x:t>dialogue_title_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이힐을 신은 사이보그 내년 복귀.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>집단 이주가 계속되고 있습니다....</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새롭게 나타난 위협 원더랜더즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"원더랜더즈" 가 당신의 보안체계에 새로운 위협으로 나타났다
+킴벌리 라 발레트 기자
+그 어ᄄᅠᆫ 복잡한 보안체제든 그것을 뚫는 것에 세상에서 가장 뛰어난이가 앨리스 래빗이라고 생각하셨다면, 이 새로 나타난 집단을 보고 생각을 바꾸시게 될겁니다. 이들은 아직까지 앨리스 래빗만큼 영향력 있는 모습을 보여주지 않았지만, 최근 퀸시 총리와 관련된 문제에 대해 굉장히 큰 목표를 가지고 있는 것처럼 보입니다.
+"우리는 이미 퀸시 이메일 네트워크를 장악했고, 1월달에 데이터베이스를 날려버릴 것이다" 라고 이 단체가 생방송 중 발표했습니다.
+"얄팍한 위협이다."
+퀸시 총리는 질문을 받자 "아무것도 숨기고 있지 않으니" 이메일 기록이 유출되던 djWJejs 이 그룹의 발표가 별 위협이 되지 않는다고 말했습니다.
+"모두들 내가 저번 달에 어ᄄᅠᆫ TV를 샀는지 정도나 알게 될 겁니다."
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
   </x:si>
   <x:si>
     <x:t>string[]</x:t>
   </x:si>
   <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>VoicePath</x:t>
   </x:si>
   <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아무 대답하지 않는다,대답한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>두둥..지금.. 배가 고픕니다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
   </x:si>
   <x:si>
     <x:t>NextDialogueId</x:t>
   </x:si>
   <x:si>
-    <x:t>새로운 세계에 접속 하셨습니다…&lt;np&gt;오랜시간 기다리셨는데..&lt;np&gt;제가 많이 늦었군요...</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_2_200,dialogue_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>용사님이시어..고생하셨군요</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100</x:t>
-  </x:si>
-  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>(name)</x:t>
   </x:si>
   <x:si>
-    <x:t>커피인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피자인가..</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일단 밥을 먹지 않고 조금 더 진행해본다!</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_300</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_200</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainstream_1_1_100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
+    <x:t>퀸시의 새로운 경제 조정안 발표에 따라 집단 이주가 계속되고 있다.
+킴벌리 라 벨레트 기자
+세계에서 가장 높은 수준의 인플레이션과 기본적인 식료품 부족 그리고 걷잡을 수 없는 폭력 범죄율 때문에 글리치 시티의 시민들은 더 나은 삶을 찾아 다른 나라로 떠나고 있습니다.
+반면, 퀸시는 이 상황을 나쁘게 받아들이고 있습니다.
+총리는 본지와의 인터뷰에서 이렇게 말했습니다. "이 도시에서 의무교욱을 받고 대학을 나왔습니다, 그런데 그 기술들을 다른 곳에서 활용하고 있죠, 이건 모욕입니다."
+모두 새로운 경제 조정안이 발표된 이후에 일어나고 있는 일입니다, 많은 전문가들이 현 상황에서는 큰 의미 없는 행동이 될 거라고 지목하였습니다.
+퀸시는 "그 작자들이 뭘 안다고 그래" 라고 결론 내렸습니다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이힐을 신은 사이보그가 내년 슈퍼 실버 선더 돔으로 돌아옵니다.
+라나스미시 기자
+인기 공연 하이힐을 신은 사이보그가 다가오는 3월 선더돔으로 돌아옵니다. 1월부터 티켓 판매에 들어간다고 합니다.
+하이힐을 신은 사이보그는 하이힐을 신은 사이보그가 테러리스트들과 싸우는 웅장한 무대 공연입니다.
+ 퀸든 헤이터 감독은 본지와의 인터뷰 중에 하이힐을 신은 사이보그가 가진 특별한 매력에 관해 설명했습니다.
+"당연히 좋아하게 되는 거 아닌가? 사이보그라고, 하이힐을 신었고, 다른 건 상관없지. 말 그대로 여태까지 아무도 본적이 없는 조합이지, 내가 만들어낸 틈새시장인거라고..."
+몇주 뒤 이곳 어그멘티드 아이에서 단독 인터뷰 전문이 공개됩니다. 꼭 확인하세요.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"포어": 저 사람 행동 좀 이상한데.
+질: 아마 이 사람은 자연법칙이고 뭐고 상관없나보지.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"포어": 떠날 거야?
+질: 널 두고 떠나진 않아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질: 알마 생각은 어ᄄᅠᆯ지 궁금한걸...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"포어": 그래서, 그 편지는 누구한테 온거야?
+질: 아무도 아냐.</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -144,6 +167,11 @@
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+    </x:font>
+    <x:font>
+      <x:name val="돋움"/>
+      <x:sz val="11"/>
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
@@ -191,12 +219,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="2">
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left>
         <x:color rgb="ff000000"/>
       </x:left>
@@ -204,13 +231,16 @@
         <x:color rgb="ff000000"/>
       </x:right>
       <x:top>
-        <x:color auto="1"/>
+        <x:color indexed="64"/>
       </x:top>
       <x:bottom>
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
-    <x:border>
+    <x:border diagonalUp="1" diagonalDown="1">
       <x:left style="thin">
         <x:color rgb="ff000000"/>
       </x:left>
@@ -223,36 +253,81 @@
       <x:bottom style="thin">
         <x:color rgb="ff000000"/>
       </x:bottom>
+      <x:diagonal>
+        <x:color indexed="64"/>
+      </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -267,17 +342,478 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
-    <x:cellStyle name="표준" xfId="0" builtinId="0"/>
+    <x:cellStyle xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="0"/>
+  <x:dxfs count="18">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd9e6fd"/>
+              <x:bgColor rgb="ffd9e6fd"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:left style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:left>
+        <x:right style="thin">
+          <x:color rgb="ffbfbfbf"/>
+        </x:right>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9d9d9"/>
+          <x:bgColor rgb="ffd9d9d9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff4285f4"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:bottom style="thin">
+          <x:color rgb="ff8db6f9"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:bottom>
+            <x:horizontal style="thin">
+              <x:color rgb="ff8db6f9"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff4285f4"/>
+              <x:bgColor rgb="ff4285f4"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="double">
+              <x:color rgb="ff4285f4"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffd9e6fd"/>
+          <x:bgColor rgb="ffd9e6fd"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
   <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
 </x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -472,21 +1008,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:R35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="26.36328125" customWidth="1"/>
     <x:col min="2" max="2" width="19.54296875" customWidth="1"/>
-    <x:col min="3" max="6" width="77.08984375" customWidth="1"/>
+    <x:col min="3" max="3" width="57.28515625" customWidth="1"/>
+    <x:col min="4" max="6" width="77.08984375" customWidth="1"/>
     <x:col min="7" max="8" width="50.7265625" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -498,28 +1033,28 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
@@ -530,38 +1065,34 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>28</x:v>
+      <x:c r="A4" s="12" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="5"/>
       <x:c r="C4" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="s">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D4" s="4"/>
+      <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="3"/>
       <x:c r="J4" s="3"/>
@@ -575,16 +1106,14 @@
       <x:c r="R4" s="3"/>
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4" t="s">
-        <x:v>27</x:v>
+      <x:c r="A5" s="12" t="s">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="5"/>
       <x:c r="C5" s="4" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>26</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D5" s="4"/>
       <x:c r="E5" s="4"/>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4"/>
@@ -601,20 +1130,18 @@
       <x:c r="R5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A6" s="4" t="s">
-        <x:v>26</x:v>
+      <x:c r="A6" s="12" t="s">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="5"/>
       <x:c r="C6" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
-      <x:c r="H6" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="H6" s="4"/>
       <x:c r="I6" s="3"/>
       <x:c r="J6" s="3"/>
       <x:c r="K6" s="3"/>
@@ -627,20 +1154,16 @@
       <x:c r="R6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4" t="s">
+      <x:c r="A7" s="12" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B7" s="4"/>
+      <x:c r="C7" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B7" s="4"/>
-      <x:c r="C7" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="D7" s="4"/>
-      <x:c r="E7" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="E7" s="4"/>
+      <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="3"/>
@@ -655,12 +1178,12 @@
       <x:c r="R7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A8" s="4" t="s">
-        <x:v>17</x:v>
+      <x:c r="A8" s="12" t="s">
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="6"/>
-      <x:c r="C8" s="6" t="s">
-        <x:v>22</x:v>
+      <x:c r="C8" s="13" t="s">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -679,20 +1202,18 @@
       <x:c r="R8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A9" s="4" t="s">
-        <x:v>18</x:v>
+      <x:c r="A9" s="12" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6" t="s">
-        <x:v>23</x:v>
+      <x:c r="C9" s="13" t="s">
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D9" s="6"/>
       <x:c r="E9" s="6"/>
       <x:c r="F9" s="6"/>
       <x:c r="G9" s="6"/>
-      <x:c r="H9" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="H9" s="4"/>
       <x:c r="I9" s="3"/>
       <x:c r="J9" s="3"/>
       <x:c r="K9" s="3"/>
@@ -706,11 +1227,11 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="7"/>
-      <x:c r="C10" s="7" t="s">
-        <x:v>25</x:v>
+      <x:c r="C10" s="14" t="s">
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
@@ -729,9 +1250,13 @@
       <x:c r="R10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A11" s="7"/>
+      <x:c r="A11" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
+      <x:c r="C11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
       <x:c r="F11" s="7"/>
@@ -749,9 +1274,13 @@
       <x:c r="R11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
+      <x:c r="A12" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="B12" s="7"/>
+      <x:c r="C12" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
       <x:c r="F12" s="6"/>
@@ -769,9 +1298,13 @@
       <x:c r="R12" s="3"/>
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
+      <x:c r="A13" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B13" s="6"/>
+      <x:c r="C13" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>
       <x:c r="F13" s="4"/>
@@ -1994,7 +2527,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="0" verticalDpi="0" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/RobbyDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/RobbyDialogue.xlsx
@@ -16,24 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <x:si>
-    <x:t>dialogue_title_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_title_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하이힐을 신은 사이보그 내년 복귀.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>집단 이주가 계속되고 있습니다....</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_title_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새롭게 나타난 위협 원더랜더즈</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">"원더랜더즈" 가 당신의 보안체계에 새로운 위협으로 나타났다
 킴벌리 라 발레트 기자
 그 어ᄄᅠᆫ 복잡한 보안체제든 그것을 뚫는 것에 세상에서 가장 뛰어난이가 앨리스 래빗이라고 생각하셨다면, 이 새로 나타난 집단을 보고 생각을 바꾸시게 될겁니다. 이들은 아직까지 앨리스 래빗만큼 영향력 있는 모습을 보여주지 않았지만, 최근 퀸시 총리와 관련된 문제에 대해 굉장히 큰 목표를 가지고 있는 것처럼 보입니다.
@@ -44,42 +26,6 @@
 </x:t>
   </x:si>
   <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TexturePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
     <x:t>퀸시의 새로운 경제 조정안 발표에 따라 집단 이주가 계속되고 있다.
 킴벌리 라 벨레트 기자
 세계에서 가장 높은 수준의 인플레이션과 기본적인 식료품 부족 그리고 걷잡을 수 없는 폭력 범죄율 때문에 글리치 시티의 시민들은 더 나은 삶을 찾아 다른 나라로 떠나고 있습니다.
@@ -89,6 +35,33 @@
 퀸시는 "그 작자들이 뭘 안다고 그래" 라고 결론 내렸습니다.</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_title_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>집단 이주가 계속되고 있습니다....</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>하이힐을 신은 사이보그가 내년 슈퍼 실버 선더 돔으로 돌아옵니다.
 라나스미시 기자
 인기 공연 하이힐을 신은 사이보그가 다가오는 3월 선더돔으로 돌아옵니다. 1월부터 티켓 판매에 들어간다고 합니다.
@@ -98,40 +71,67 @@
 몇주 뒤 이곳 어그멘티드 아이에서 단독 인터뷰 전문이 공개됩니다. 꼭 확인하세요.</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_detail1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_detail1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_detail1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_003</x:t>
+    <x:t>"포어": 떠날 거야?
+질: 널 두고 떠나진 않아.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질: 알마 생각은 어떨지 궁금한걸...</x:t>
   </x:si>
   <x:si>
     <x:t>"포어": 저 사람 행동 좀 이상한데.
 질: 아마 이 사람은 자연법칙이고 뭐고 상관없나보지.</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_talk_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"포어": 떠날 거야?
-질: 널 두고 떠나진 않아.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질: 알마 생각은 어ᄄᅠᆯ지 궁금한걸...</x:t>
-  </x:si>
-  <x:si>
     <x:t>"포어": 그래서, 그 편지는 누구한테 온거야?
 질: 아무도 아냐.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TexturePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VoicePath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새롭게 나타난 위협 원더랜더즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이힐을 신은 사이보그 내년 복귀.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1021,7 +1021,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -1033,63 +1033,63 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="5"/>
       <x:c r="C4" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
       <x:c r="G4" s="4"/>
@@ -1107,11 +1107,11 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="5"/>
       <x:c r="C5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D5" s="4"/>
       <x:c r="E5" s="4"/>
@@ -1131,11 +1131,11 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="12" t="s">
-        <x:v>0</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="5"/>
       <x:c r="C6" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
@@ -1155,11 +1155,11 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>22</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="4"/>
       <x:c r="C7" s="12" t="s">
-        <x:v>19</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
@@ -1179,11 +1179,11 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>21</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="6"/>
       <x:c r="C8" s="13" t="s">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -1203,11 +1203,11 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="12" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="6"/>
       <x:c r="C9" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D9" s="6"/>
       <x:c r="E9" s="6"/>
@@ -1227,11 +1227,11 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="7"/>
       <x:c r="C10" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D10" s="7"/>
       <x:c r="E10" s="7"/>
@@ -1251,11 +1251,11 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="7"/>
       <x:c r="C11" s="14" t="s">
-        <x:v>29</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D11" s="7"/>
       <x:c r="E11" s="7"/>
@@ -1275,11 +1275,11 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="7"/>
       <x:c r="C12" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
@@ -1299,11 +1299,11 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="6"/>
       <x:c r="C13" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>

--- a/JsonConverter/ExcelFiles/RobbyDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/RobbyDialogue.xlsx
@@ -16,16 +16,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <x:si>
-    <x:t xml:space="preserve">"원더랜더즈" 가 당신의 보안체계에 새로운 위협으로 나타났다
-킴벌리 라 발레트 기자
-그 어ᄄᅠᆫ 복잡한 보안체제든 그것을 뚫는 것에 세상에서 가장 뛰어난이가 앨리스 래빗이라고 생각하셨다면, 이 새로 나타난 집단을 보고 생각을 바꾸시게 될겁니다. 이들은 아직까지 앨리스 래빗만큼 영향력 있는 모습을 보여주지 않았지만, 최근 퀸시 총리와 관련된 문제에 대해 굉장히 큰 목표를 가지고 있는 것처럼 보입니다.
-"우리는 이미 퀸시 이메일 네트워크를 장악했고, 1월달에 데이터베이스를 날려버릴 것이다" 라고 이 단체가 생방송 중 발표했습니다.
-"얄팍한 위협이다."
-퀸시 총리는 질문을 받자 "아무것도 숨기고 있지 않으니" 이메일 기록이 유출되던 djWJejs 이 그룹의 발표가 별 위협이 되지 않는다고 말했습니다.
-"모두들 내가 저번 달에 어ᄄᅠᆫ TV를 샀는지 정도나 알게 될 겁니다."
-</x:t>
-  </x:si>
-  <x:si>
     <x:t>퀸시의 새로운 경제 조정안 발표에 따라 집단 이주가 계속되고 있다.
 킴벌리 라 벨레트 기자
 세계에서 가장 높은 수준의 인플레이션과 기본적인 식료품 부족 그리고 걷잡을 수 없는 폭력 범죄율 때문에 글리치 시티의 시민들은 더 나은 삶을 찾아 다른 나라로 떠나고 있습니다.
@@ -35,31 +25,31 @@
 퀸시는 "그 작자들이 뭘 안다고 그래" 라고 결론 내렸습니다.</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_title_1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_detail1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>집단 이주가 계속되고 있습니다....</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_title_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_detail1_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_detail1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_title_1_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionDialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>dialogue_talk_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>새롭게 나타난 위협 원더랜더즈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionNameList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하이힐을 신은 사이보그 내년 복귀.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_talk_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NextDialogueId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CharacterDataId</x:t>
   </x:si>
   <x:si>
     <x:t>하이힐을 신은 사이보그가 내년 슈퍼 실버 선더 돔으로 돌아옵니다.
@@ -71,67 +61,77 @@
 몇주 뒤 이곳 어그멘티드 아이에서 단독 인터뷰 전문이 공개됩니다. 꼭 확인하세요.</x:t>
   </x:si>
   <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t>"포어": 떠날 거야?
 질: 널 두고 떠나진 않아.</x:t>
   </x:si>
   <x:si>
-    <x:t>질: 알마 생각은 어떨지 궁금한걸...</x:t>
-  </x:si>
-  <x:si>
     <x:t>"포어": 저 사람 행동 좀 이상한데.
 질: 아마 이 사람은 자연법칙이고 뭐고 상관없나보지.</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">"원더랜더즈" 가 당신의 보안체계에 새로운 위협으로 나타났다
+킴벌리 라 발레트 기자
+그 어떠한복잡한 보안체제든 그것을 뚫는 것에 세상에서 가장 뛰어난이가 앨리스 래빗이라고 생각하셨다면, 이 새로 나타난 집단을 보고 생각을 바꾸시게 될겁니다. 이들은 아직까지 앨리스 래빗만큼 영향력 있는 모습을 보여주지 않았지만, 최근 퀸시 총리와 관련된 문제에 대해 굉장히 큰 목표를 가지고 있는 것처럼 보입니다.
+"우리는 이미 퀸시 이메일 네트워크를 장악했고, 1월달에 데이터베이스를 날려버릴 것이다" 라고 이 단체가 생방송 중 발표했습니다.
+"얄팍한 위협이다."
+퀸시 총리는 질문을 받자 "아무것도 숨기고 있지 않으니" 이메일 기록이 유출되던 어쩌던 이 그룹의 발표가 별 위협이 되지 않는다고 말했습니다.
+"모두들 내가 저번 달에 어떤 TV를 샀는지 정도나 알게 될 겁니다."
+</x:t>
+  </x:si>
+  <x:si>
     <x:t>"포어": 그래서, 그 편지는 누구한테 온거야?
 질: 아무도 아냐.</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>TexturePath</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
+    <x:t>VoicePath</x:t>
   </x:si>
   <x:si>
     <x:t>string[]</x:t>
   </x:si>
   <x:si>
-    <x:t>VoicePath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>새롭게 나타난 위협 원더랜더즈</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SelectionNameList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_talk_1_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하이힐을 신은 사이보그 내년 복귀.</x:t>
+    <x:t>dialogue_detail1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질: 알마 생각은 어떨지 궁금한걸...</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_detail1_1_000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SelectionDialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_title_1_1_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>집단 이주가 계속되고 있습니다....</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NextDialogueId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CharacterDataId</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1033,63 +1033,63 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A4" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="5"/>
       <x:c r="C4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D4" s="4"/>
       <x:c r="G4" s="4"/>
@@ -1107,11 +1107,11 @@
     </x:row>
     <x:row r="5" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A5" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="5"/>
       <x:c r="C5" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D5" s="4"/>
       <x:c r="E5" s="4"/>
@@ -1131,11 +1131,11 @@
     </x:row>
     <x:row r="6" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A6" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="5"/>
       <x:c r="C6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="4"/>
       <x:c r="E6" s="4"/>
@@ -1155,11 +1155,11 @@
     </x:row>
     <x:row r="7" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B7" s="4"/>
       <x:c r="C7" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="4"/>
       <x:c r="E7" s="4"/>
@@ -1179,11 +1179,11 @@
     </x:row>
     <x:row r="8" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>3</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B8" s="6"/>
       <x:c r="C8" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="6"/>
@@ -1203,11 +1203,11 @@
     </x:row>
     <x:row r="9" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A9" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B9" s="6"/>
       <x:c r="C9" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="6"/>
       <x:c r="E9" s="6"/>
@@ -1227,7 +1227,7 @@
     </x:row>
     <x:row r="10" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="7"/>
       <x:c r="C10" s="14" t="s">
@@ -1251,7 +1251,7 @@
     </x:row>
     <x:row r="11" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A11" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="7"/>
       <x:c r="C11" s="14" t="s">
@@ -1275,11 +1275,11 @@
     </x:row>
     <x:row r="12" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A12" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="7"/>
       <x:c r="C12" s="7" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="6"/>
@@ -1299,11 +1299,11 @@
     </x:row>
     <x:row r="13" spans="1:18" ht="15.75" customHeight="1">
       <x:c r="A13" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B13" s="6"/>
       <x:c r="C13" s="13" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="4"/>
       <x:c r="E13" s="4"/>
